--- a/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/序章1.xlsx
+++ b/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/序章1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="75">
   <si>
     <t>ID</t>
   </si>
@@ -337,7 +337,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,13 +350,6 @@
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -824,175 +817,172 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1314,7 +1304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="14.6" customWidth="1"/>
@@ -1485,7 +1475,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" ht="15.5" spans="1:12">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>1005</v>
       </c>
@@ -1496,8 +1486,8 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="5">
-        <v>0.542361111111111</v>
+      <c r="G7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1516,7 +1506,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1535,7 +1525,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1547,14 +1537,14 @@
         <v>1008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1573,7 +1563,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1585,14 +1575,14 @@
         <v>1010</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1604,14 +1594,14 @@
         <v>1011</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1622,60 +1612,60 @@
       <c r="A14">
         <v>1012</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="B14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" ht="28" spans="1:12">
       <c r="A15">
         <v>1013</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" ht="28" spans="1:12">
       <c r="A16">
         <v>1014</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" ht="28" spans="1:11">
+        <v>34</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>1015</v>
       </c>
@@ -1686,8 +1676,8 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="7" t="s">
-        <v>34</v>
+      <c r="G17" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -1698,20 +1688,22 @@
       <c r="A18">
         <v>1016</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
@@ -1725,16 +1717,14 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" ht="56" spans="1:11">
       <c r="A20">
         <v>1018</v>
       </c>
@@ -1745,15 +1735,15 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>38</v>
+      <c r="G20" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" ht="56" spans="1:11">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>1019</v>
       </c>
@@ -1762,17 +1752,19 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="6" t="s">
-        <v>39</v>
+      <c r="G21" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" ht="56" spans="1:11">
       <c r="A22">
         <v>1020</v>
       </c>
@@ -1785,69 +1777,67 @@
         <v>40</v>
       </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>41</v>
+      <c r="G22" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" ht="56" spans="1:11">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>1021</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
       <c r="E23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
         <v>1022</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
         <v>1023</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="8" t="s">
-        <v>45</v>
+      <c r="G25" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1859,14 +1849,16 @@
         <v>1024</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="8" t="s">
-        <v>47</v>
+      <c r="G26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -1878,101 +1870,99 @@
         <v>1025</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F27" s="2"/>
-      <c r="G27" s="2" t="s">
-        <v>25</v>
+      <c r="G27" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" ht="14.5" spans="1:11">
       <c r="A28">
         <v>1026</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="8" t="s">
-        <v>49</v>
+      <c r="G28" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" ht="14.5" spans="1:11">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>1027</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="8" t="s">
-        <v>50</v>
+      <c r="G29" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
         <v>1028</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K30" s="2"/>
+      <c r="B30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
         <v>1029</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
+      <c r="B31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
@@ -1985,34 +1975,34 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="8" t="s">
-        <v>54</v>
+      <c r="G32" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="I32" s="3"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" ht="28" spans="1:11">
       <c r="A33">
         <v>1031</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="2"/>
+      <c r="B33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" ht="28" spans="1:11">
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>1032</v>
       </c>
@@ -2023,8 +2013,8 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="10" t="s">
-        <v>56</v>
+      <c r="G34" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -2043,7 +2033,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -2054,34 +2044,34 @@
       <c r="A36">
         <v>1034</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
+      <c r="B36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
         <v>1035</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="8" t="s">
-        <v>59</v>
+      <c r="G37" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -2097,10 +2087,12 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+      <c r="E38" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F38" s="2"/>
-      <c r="G38" s="8" t="s">
-        <v>60</v>
+      <c r="G38" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -2117,11 +2109,11 @@
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="F39" s="2"/>
-      <c r="G39" s="8" t="s">
-        <v>62</v>
+      <c r="G39" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -2138,11 +2130,11 @@
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="8" t="s">
-        <v>63</v>
+      <c r="G40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -2159,95 +2151,95 @@
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" ht="14.5" spans="1:11">
       <c r="A42">
         <v>1040</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F42" s="2"/>
-      <c r="G42" s="2" t="s">
-        <v>64</v>
+      <c r="G42" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" ht="14.5" spans="1:11">
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>1041</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F43" s="2"/>
-      <c r="G43" s="8" t="s">
-        <v>65</v>
+      <c r="G43" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" ht="14.5" spans="1:11">
       <c r="A44">
         <v>1042</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F44" s="2"/>
-      <c r="G44" s="8" t="s">
-        <v>66</v>
+      <c r="G44" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" ht="14.5" spans="1:11">
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>1043</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="8" t="s">
-        <v>67</v>
+      <c r="G45" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -2258,62 +2250,60 @@
       <c r="A46">
         <v>1044</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="B46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+    </row>
+    <row r="47" ht="28" spans="1:11">
       <c r="A47">
         <v>1045</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" ht="28" spans="1:11">
+      <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>1046</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="B48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
     </row>
     <row r="49" spans="1:11">
       <c r="A49">
@@ -2327,30 +2317,36 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
     </row>
-    <row r="50" spans="1:11">
-      <c r="B50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
+    <row r="50" ht="42" spans="1:11">
+      <c r="A50">
+        <v>1048</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
       <c r="K50" s="3"/>
     </row>
-    <row r="51" ht="42" spans="1:11">
+    <row r="51" spans="1:11">
+      <c r="A51">
+        <v>1049</v>
+      </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
@@ -2358,27 +2354,11 @@
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="B52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2" t="s">
+      <c r="K51" s="2" t="s">
         <v>74</v>
       </c>
     </row>
